--- a/artfynd/A 19728-2025 artfynd.xlsx
+++ b/artfynd/A 19728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127101003</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19728-2025 artfynd.xlsx
+++ b/artfynd/A 19728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127101003</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19728-2025 artfynd.xlsx
+++ b/artfynd/A 19728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127101003</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19728-2025 artfynd.xlsx
+++ b/artfynd/A 19728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127101003</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19728-2025 artfynd.xlsx
+++ b/artfynd/A 19728-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128899907</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91454</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>112</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gullabborrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>592584</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6984430</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19728-2025 artfynd.xlsx
+++ b/artfynd/A 19728-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128899907</v>
       </c>
       <c r="B3" t="n">
-        <v>91454</v>
+        <v>91458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19728-2025 artfynd.xlsx
+++ b/artfynd/A 19728-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128899907</v>
       </c>
       <c r="B3" t="n">
-        <v>91458</v>
+        <v>91463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19728-2025 artfynd.xlsx
+++ b/artfynd/A 19728-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128899907</v>
       </c>
       <c r="B3" t="n">
-        <v>91470</v>
+        <v>91473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19728-2025 artfynd.xlsx
+++ b/artfynd/A 19728-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128899907</v>
       </c>
       <c r="B3" t="n">
-        <v>91473</v>
+        <v>91476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19728-2025 artfynd.xlsx
+++ b/artfynd/A 19728-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128899907</v>
       </c>
       <c r="B3" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19728-2025 artfynd.xlsx
+++ b/artfynd/A 19728-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128899907</v>
       </c>
       <c r="B3" t="n">
-        <v>91482</v>
+        <v>91489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19728-2025 artfynd.xlsx
+++ b/artfynd/A 19728-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128899907</v>
       </c>
       <c r="B3" t="n">
-        <v>91489</v>
+        <v>91491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19728-2025 artfynd.xlsx
+++ b/artfynd/A 19728-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128899907</v>
       </c>
       <c r="B3" t="n">
-        <v>91491</v>
+        <v>91494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19728-2025 artfynd.xlsx
+++ b/artfynd/A 19728-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128899907</v>
       </c>
       <c r="B3" t="n">
-        <v>91494</v>
+        <v>91496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19728-2025 artfynd.xlsx
+++ b/artfynd/A 19728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127101003</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19728-2025 artfynd.xlsx
+++ b/artfynd/A 19728-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127101003</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19728-2025 artfynd.xlsx
+++ b/artfynd/A 19728-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127101003</v>
+        <v>128899907</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnmyran, Jmt</t>
+          <t>Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592551</v>
+        <v>592584</v>
       </c>
       <c r="R2" t="n">
-        <v>6984416</v>
+        <v>6984430</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899907</v>
+        <v>127101003</v>
       </c>
       <c r="B3" t="n">
-        <v>91496</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Jmt</t>
+          <t>Gullabborrtjärnmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592584</v>
+        <v>592551</v>
       </c>
       <c r="R3" t="n">
-        <v>6984430</v>
+        <v>6984416</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 19728-2025 artfynd.xlsx
+++ b/artfynd/A 19728-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899907</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,8 +886,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127101003</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>